--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,418 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129281233</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flogen Tretåig hackspett ringhack 2, Flogen Tretåig hackspett ringhack 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>508227</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6686306</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129281192</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flogen Tretå Ringhack 1, Flogen Tretå Ringhack 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>508298</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6686259</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, färskt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129281181</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508212</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6686282</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129281129</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508296</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6686234</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>91517</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129281233</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129281192</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,62 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R5" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,48 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R6" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,48 +1005,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R5" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,62 +1116,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R6" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,62 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R5" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,48 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R6" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,48 +1005,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B5" t="n">
-        <v>91524</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R5" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,62 +1116,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R6" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1119,7 +1119,7 @@
         <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,62 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R5" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,48 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>91527</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R6" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>91527</v>
+        <v>91529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,48 +1005,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B5" t="n">
-        <v>91529</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R5" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,62 +1116,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R6" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,62 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R5" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,48 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R6" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,48 +1005,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B5" t="n">
-        <v>91534</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R5" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,62 +1116,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R6" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,62 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91537</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R5" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,48 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>91534</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R6" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,48 +1005,62 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B5" t="n">
-        <v>91537</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R5" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,62 +1116,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91537</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R6" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -1005,62 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281181</v>
+        <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91537</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508212</v>
+        <v>508296</v>
       </c>
       <c r="R5" t="n">
-        <v>6686282</v>
+        <v>6686234</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,48 +1102,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281129</v>
+        <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>91537</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508296</v>
+        <v>508212</v>
       </c>
       <c r="R6" t="n">
-        <v>6686234</v>
+        <v>6686282</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129281233</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129281192</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>91537</v>
+        <v>91565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129281233</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129281192</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>91565</v>
+        <v>91571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129281233</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129281192</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129281129</v>
       </c>
       <c r="B5" t="n">
-        <v>91571</v>
+        <v>91572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>129281181</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43226-2025 artfynd.xlsx
+++ b/artfynd/A 43226-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>68175570</v>
       </c>
       <c r="B2" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508199.9042059754</v>
+        <v>508200</v>
       </c>
       <c r="R2" t="n">
-        <v>6686319.967972979</v>
+        <v>6686320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2017-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,45 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129281233</v>
+        <v>129281129</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett ringhack 2, Flogen Tretåig hackspett ringhack 2, Dlr</t>
+          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508227</v>
+        <v>508296</v>
       </c>
       <c r="R3" t="n">
-        <v>6686306</v>
+        <v>6686234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129281192</v>
+        <v>129281181</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,17 +911,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flogen Tretå Ringhack 1, Flogen Tretå Ringhack 1, Dlr</t>
+          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508298</v>
+        <v>508212</v>
       </c>
       <c r="R4" t="n">
-        <v>6686259</v>
+        <v>6686282</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran, färskt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,48 +994,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129281129</v>
+        <v>129281192</v>
       </c>
       <c r="B5" t="n">
-        <v>91572</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flogen Rävticka , Flogen Rävticka , Dlr</t>
+          <t>Flogen Tretå Ringhack 1, Flogen Tretå Ringhack 1, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508296</v>
+        <v>508298</v>
       </c>
       <c r="R5" t="n">
-        <v>6686234</v>
+        <v>6686259</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,6 +1065,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, färskt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129281181</v>
+        <v>129281233</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,34 +1124,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flogen Tretåig hackspett, Flogen Tretåig hackspett, Dlr</t>
+          <t>Flogen Tretåig hackspett ringhack 2, Flogen Tretåig hackspett ringhack 2, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508212</v>
+        <v>508227</v>
       </c>
       <c r="R6" t="n">
-        <v>6686282</v>
+        <v>6686306</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,6 +1167,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
